--- a/nir_barket_diary_q2.xlsx
+++ b/nir_barket_diary_q2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gil1f\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2829DDDB-762D-4801-BC19-47D0C6007954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AD5A8C-6695-4F5E-99F6-C14F945B9A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="20098" windowHeight="10671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="853">
   <si>
     <t>תאריך התחלה</t>
   </si>
@@ -1282,6 +1282,1318 @@
   </si>
   <si>
     <t xml:space="preserve">שיחה עם עיתונאי </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> אזכרה נדב מרחב</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> אזכרה</t>
+  </si>
+  <si>
+    <t>ההזמנה עודכנה  השר ניר ברקת הצגת תוכנית של משרד הכלכלה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  מטה מול מטה עם אלקין </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  רון תומר וחגי אדרי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחת טלפון ליז מונטיליו</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פנינה לב </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ניחום אבלים ליאור קצב </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ניר בן חיים עם מלכי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ניחום אבלים משפחתו של סולי בסוס ז"ל </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> מפגש עם משה בן שמעון </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  מפגש חברים אצל מימון לוי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  זום שירה לב עמי + מנהל המוצר  עלויות הפרויקט </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ועדת שרים למינויים בשירות החוץ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחת טלפון עם ראשת מועצה אזורית אשכול מיכל עוזיהו</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שי חג'ג</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לשי חג'ג</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחות פוליטיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לפגישה עם עיריית ערד</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנסת ספר תורה ע"ש דוד לוי ז"ל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  תעשייה  חקלאות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ח"כ יולי אדלשטיין</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לשיחה טלפונית עם סגן הקאנצלר בגרמניה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  מורן אזולאי</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פ.ע תקשורת </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לנאום בכנס חקלאות עם כותבת הנאומים</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה עם הצוות הפוליטי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם אדם מילא (מערכת מאיה)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם עיריית ערד </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ראיון עם פתחי וזמרי גלי ישראל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לראיון עם פתחי וזמרי גלי ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  אילן בן סעדון</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ארוחת צהריים </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה אישית עם ראש העיר ברוט </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  כנס של משרד החקלאות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  בר מצווה נעם ינון הבן של אמנון כהן נציג הליכוד בעיריית באר שבע </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה מקצועית בעיריית יהוד </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה מקצועית וסיור בעיריית בת ים </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> מעבר לו"ז </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחה וירטואלית עם סגן הקאנצלר גרמניה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לראש מפאת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם אריה ויסמן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  יוסי פדידה מפגש חברים במסעדת שלה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לסיור במועצה מקומית זרזיר </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  דיון במועצת בית זרזיר עם ראש המועצה  עאטף גריפאת </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  נסיעה לקריית מוצקין</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  נסיעה למרכז הטכנולוגי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  משיח עמר מפגש חברים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ביקור במרכז הטכנולוגי וארוחת צהריים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ראש מפא"ת </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  חתונה של הבן של יוסי ברבי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  יום הולדתו של ראובן גבריאלי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לראש העיר באר שבע</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לשיחה עם השר הוויאטנמי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הזמנה לישיבת מרכז הליכוד</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ישיבת צוות פוליטית </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פ.ע שלמה לוי עדכוני מנהלת </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   סימון מחירים</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> עפיף עבד בנושא דרוזים </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הערכות החזרת עובדים לצפון </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  דוד אבבה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שי מלכה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לשולחן עגול  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה עם מוטי שרף </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ראיון בשולחן עגול עם נגה ניר נאמן ומוטי שרף על מיתוג ישראל בעולם ומצבה הבינלאומי דגש צמיחה וכלכלה</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> סטטוס נסיעה להודו </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחה עם השר המקביל הויאטנמי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לנאום לישיבה המשותפת של נשיאות במגזר העסקי והנהגת ההסתדרות בצפון עם כתבת הנאומים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם ראש עיריית באר שבע רוביק דנילוביץ'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  סטטוס קלסטרים</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> שיחת עדכון דאבוס </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הילולה של הרב מזוז </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ניחום אבלים של רס״ם אלכסנדר פדורנקו ז״ל </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ניחום אבלים משפחתו של סמ״ר קנאו קאסה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ינון מגל  כתב ערוץ  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  בועז טביב  משה אחרק</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ביקור באוני' ת"א, הקמת מתקן ייצור ווקטורים וויראליים  חיסוני מגפות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחת ועידה עלי בינג בנושא דיגיטל</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פע יאיר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הערכות החזרת עובדים לצפון </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לסיור בצפון </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ג'וחא</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פורום מועד אוקטובר </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> שיחת המשך עם שירה לב עמי + מנהל המוצר  עלויות הפרויקט </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  נסיעה לאולם "מאגיה" </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ביקור במועצות מג'דל שמס, מסעדה, בוקעתא, עין קיניא</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> נסיעה לרמת הגולן </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ביקור במרכז החקלאי צמח </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  חתונה לבן של שמעון סויסה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ישיבה משותפת של נשיאות המגזר העסקי והנהגת ההסתדרות בצפון </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  חתונה משפחת בניון, אסף ואלמוג </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לדאבוס</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פ"ע עם החשב הכללי</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> קובי זריהן </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכשרות מעסיקים  הצגת מיזמים משותפים </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לנטפליקס </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ניחום אבלים אהרון חשב המשרד על מות אביו </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ניחום אבלים פבריס על מות אביו  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> קלנר </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ללו זוהר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם  Madeleine de Cock Buning +  Larry Tanz + שני VP  נטפליקס</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  דוד גולן </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> תורנות שרים במליאה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  חתונה לבן של דורית ריכטר</t>
+  </si>
+  <si>
+    <t>נסיעת שר לדאבוס</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Panel Insights over Lunch FaultLines and Flashpoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Transfer to Congress center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Briefing with the Israeli Ambassador to the UN and international organizations, Geneva Mr. Daniel Meron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Arrival at Zurich Airport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Dinner at The Hotel Restaurant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Transfer to the hotel and refresh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Fabrizio Palermo, CEO of Acea (Italy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Transfer to the next meeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Dr. Shamsheer Vaylil, Founder and Chairman of Burjeel Holdings (UAE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Session US Economy in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  CNBC – Interview (TV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Girish Ramachandran (India) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Arrival at Davos &amp; Checkin and Refresh in the Room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  המראה לציריך </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  אירוע עם הנשיא הרצוג</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם Philippe Amon (Switzerland)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  חתונה לבן של הרב ניר בן ארצי  נוריה ובתל אל</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Transfer to the helicopter landing point</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Transfer to the hotel refresh and checkout </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Mr. Jayant Chaudhary, Minister of State (IC) of Skill Development and Entrepreneurship; and Minister of State of Education, India (India)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Sajjan Jindal – chairman of JSW group (India)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Lunch </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  טיסת אל על </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Arrival at Zurich airport</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Toshifumi Yoshizaki, SEVP and CDO, NEC (Japan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Interview  NDTV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Pichai Naripthaphan, Thailand’s Minister of Commerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Transfer to the next meeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ראיון עם דר שפיגל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Breakfast and briefing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ms. Cristina Roque, Secretary of Trade and Industry, Philippines </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Interview Reuters    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Elizabeth “Lally” Graham Weymouth, senior associate editor of The Washington Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jacob Safra, chairman of Safra bank </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Akira Shimada, President and CEO of NTT (Japan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> שבי ברכה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> יוגב פלד + גבי מירל + אריק בן ישי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  חאלד אבו עגאג סגן העיר כספייה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  יוסי פדידה וציון לנקרי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שיחות פוליטיות </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לאלקין </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לנאום בדימונה</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ציון חסיד</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה טלפונית לראיון היום </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  נסיעה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הפטריוטים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שי שגיא  פורום ארגוני הימין הציוני </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ניחום אבלים שלום אדרי </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ששון גואטה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   פגישת המשך השר זאב אלקין+ שר הכלכלה והתעשייה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">יום הולדת הפתעה ליורם יזדי </t>
+  </si>
+  <si>
+    <t>ההזמנה עודכנה  פגישת המשך השר זאב אלקין+ שר הכלכלה והתעשייה  ניר ..., יום ב׳  בינואר ,  PM   PM (GMT‎+‎) (luz.sar@economy.gov.il)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  דיון בנושא הקמת צוות לקידום היבטי הדיגיטל, הדאטה והבינה המלאכותית בתחום התעסוקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ראיון עם אמיר איבגי גל"צ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לרדיו </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> קפה עם אמנון </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> איתמר ראש המועצה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישות עם נתיב העשרה, קיבוץ כרמיה, קיבוץ יד מרדכי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ארוחת ערב עם קבוצה של אנשי עסקים מבריטניה וארה"ב, יום שלישי,  בינו׳ ·  – </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> קלאסטר סינרגי   הראל רם </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> קלאסטר  חממת אינגב  ארנון</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> אירוע השקה חגיגי של מרכז החדשנות דרום  בהובלת ראש העיר דימונה מר בני ביטון </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחת רקע עם עמיאל ירחי ממקור ראשון </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחת רקע עם יובל שגב מגל"צ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> בן ציון כוכבי </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ניחום אבלים עופר בראשי </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> יוחנן נקטלוב</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> תורנות שרים במליאה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> עובד חוגי חמכז תל אביב דרום </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם בילי רובין חברת מרכז תל אביב צפון</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לשגריר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם אריאל סנדר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם יחיאל טוהמי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הדר מילר ערוץ  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פ"ע רון תומר </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> שגריר יפן </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> שלמה לוי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לשר החוץ של ארגנטינה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> מעבר מכתבים עם ברק</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחה טלפונית עם מבקר המדינה מר מתניהו אנגלמן</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> דיון בג"צ מיכל כהן </t>
+  </si>
+  <si>
+    <t xml:space="preserve">נסיעה לבית השגריר </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שר החוץ של ארגנטינה GERARDO WERTHEIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> בני כשריאל </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> גיא יפרח </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחת הכנה לפגישה עם ראש עיריית שדרות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ניחום אבלים יאיר כץ (אבא של אשתו)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ניחום אבלים שמחה רוטמן במות אביו</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> לידיעה אירוע פרידה מנציב שירות המדינה  פרופ' דניאל הרשקוביץ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> חיים אוליאל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "שותפות לשירות עם דורית ריכטר " </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ראש העיר גבעת זאב יוסף אסרף </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> תורנות שרים במילאה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה טלפונית לשיחה עם שר הכלכלה ההודי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחה טלפונית עם שר הכלכלה ההודי </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ביקור קלאסטרים ivally </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  סיור במכון הMRI </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה מקצועית עם מועצה אזורית משגב ועם ראש המועצה דני עברי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  עיריית כפר קרע </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  עיריית כרמיאל</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ועידה עם הנציב (הדר מחברת)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פגישה עם מוטי קידר </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> מאיר בן שבת </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישת היכרות עם חברת ייעוץ KPMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פ.ע מנכ"ל + תקציב המשרד </t>
+  </si>
+  <si>
+    <t xml:space="preserve">לו"ז משלחת  Arrival at respective hotels </t>
+  </si>
+  <si>
+    <t>לו"ז שר   Departure from Tel Aviv</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Checkin at the ShangriLa Eros Hotel</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Travel to ShangriLa Eros Hotel</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Landing in New Delhi Airport</t>
+  </si>
+  <si>
+    <t>הודו</t>
+  </si>
+  <si>
+    <t>לו"ז שר    on  interview with Mr. Parikshit Luthra Senior Editor &amp; Delhi Bureau Chief, CNBC TV  ( mins standing interview)</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Gala Dinner</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Travel to The Lalit Hotel</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Mutual Press Statement by both Ministers</t>
+  </si>
+  <si>
+    <t>לו"ז שר   CEO Forum</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Travel to Vanijya Bhawan</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Meeting with Mr. Sanjiv Puri CMD, ITC Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לו"ז שר   Meeting with Mr. Abhinav Dhall Group Head, Dabur </t>
+  </si>
+  <si>
+    <t>לו"ז שר   Meeting with Mr. Rajan Bharti Mittal, Vice Chairman, Bharti Enterprises</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Travel to Shangri LaEros</t>
+  </si>
+  <si>
+    <t>לו"ז שר  –  Inaugural Ceremony (with Minister Piyush Goyal)</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Briefing of Israeli companies by the Minister</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Travel to The Lalit</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Breakfast with Mr. Reuven Azar, Ambassador of Israel to India and Natasha Zangin, Economic Counsellor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לו"ז שר   Free time </t>
+  </si>
+  <si>
+    <t>לו"ז שר   Press Briefing with Israeli Journalists</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Meeting with Dr. Naresh Trehan CMD, Medanta</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Lunch and Networking at Business Forum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לו"ז שר   Meeting with Mr. Aditya Shriram, Dty MD, DCM Shriram </t>
+  </si>
+  <si>
+    <t xml:space="preserve">לו"ז שר   Meeting with Mr. Naveen Jindal,Chairman, JSPL </t>
+  </si>
+  <si>
+    <t>לו"ז שר   Travel to Man Singh Road</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Dinner</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Travel to ShangriLa Eros</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Meeting with Mr Jayant Chaudhary Minister of Skill Development and Entrepreneurship</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Travel to Kaushal Bhawan</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Meeting with Mr. Rajiv Singh, Chairman, DLF</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Travel to DLF Office</t>
+  </si>
+  <si>
+    <t>לו"ז שר     Mr. Dipanjan Roy Chaudhury, Diplomatic Editor , The Economic Times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לו"ז שר   TBD </t>
+  </si>
+  <si>
+    <t>לו"ז שר   Meeting with Dr. Ashutosh Raghuvanshi, CEO, Fortis Healthcare</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Meeting with Dr. Vikas Kumar MD, DMRC</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Lunch</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Media Interview with Mr. Zakka Jacob, Managing Editor, CNNNews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לו"ז שר   Travel to Sector , Noida </t>
+  </si>
+  <si>
+    <t>לו"ז שר   Mr. Sachin Parashar Senior Assistant Editor (Strategic Affairs) The Times of India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לו"ז שר   Meeting with Mr. Nishant Arya, ViceChairman, JBM _x000D_
+ _x000D_
+</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Breakfast meeting with Mr. Sunil Kant Munjal, CMD, Hero Corp</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Travel to Taj Mahal Hotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>לו"ז שר   Arrival at New Delhi Airport</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Travel to New Delhi Airport</t>
+  </si>
+  <si>
+    <t>לו"ז שר   Check out from Hote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  טיסת חזור לישראל  מס' טיסה LY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  כנס בראשות ראש המועצה האזורית מעלה יוסף  שמעון גואטה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הכנה לנאום בפורום הסגנים </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> מוטי קידר ויצחק מגרפתה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ליאור אזולאי</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> טיסה לאילת </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  כנס ההשתלמות השנתי של הפורום סגנים מ"מ ראשי הרשויות  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פ.ע מנכ"ל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לסיור בירוחם </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> טיסה חזור לנתב"ג</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> אלי לנקרי  ראש העיר אילת </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> אחד על אחד עם ראש עיריית ירוחם  נילי אהרון</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> מטה מול מטה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה עם יזמית הפרוייקט "סקייטק"  אורה סופר</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> טקס חניכה של הפרויקט "סקייטק"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ניחום אבלים יו"ר סניף הליכוד דימונה שמעון שטרית על מות אחיו </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> סיור ירוחם </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ראש העיר אשדוד יחיאל לסרי </t>
+  </si>
+  <si>
+    <t>שחר תורג׳מן נשיא לשכות המסחר וגילית רובינשטיין מנכלית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  חתונה הבן של איציק ונונו </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ניחום אבלים דורון תורגמן</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> יו״ר הקונגרס הבינלאומי לתעשיינים וקבלנים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  תורנות מליאה עד לתום הישיבה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  קובי זריהן ממונה רשות להגנת הצרכן </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> זום עם זמביש </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה עם הכותבת נאומים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחות פוליטיות עם משי </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> יועצי KPMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פבל ילזרוב עם פורום הקווקזים בליכוד </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  עדכון קלסטרים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לבריסל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישת המשך עם השר אלקין </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ישיבת הנהלה מורחבת </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  זום  תהילה ורון ודני טל  קנאביס</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ארוחת צהרים דדה אבן צור, ראש העיר קרית ים</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> אימו של אורן שאול ז"ל</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> נסיעה לפוריה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> קפה עם אחמד דראוושה  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> סיור במפעל אימקו יחד עם ראש העיר נשר  רועי לוי </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> דוד עציוני, אלעד אטיאס וזאב זוננסון</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  כנס ראשי המועצות האזוריות וסגניהם, התשפ"ה</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> רפי ונציה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> מתי טוכפלד ישראל היום וגלי ישראל </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> שחר גליק  גל"צ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  אמיר אטינגר ישראל היום</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  איציק בן לולו (אב שכול) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ניחום אבלים משפחתו של החטוף עודד ליפשיץ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> זום הכנה לראיון</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  מפגש אילן ויואל כהן , הלן מזוז וחברי מרכז</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> צהריים עם ישראל כץ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחה עם ההורים של החטוף אלון אוהל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  נחיתה בבריסל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  צ'ק אין במלון </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  טיסה לבריסל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">טיסה לבריסל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שיחה טלפונית עם כתב תכנון ונדל"ן של כלכליסט  גיא נרדי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  אירוע חשיפת סטארטאפים בתחום האגרוטק למשקיעים (לידיעה)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ארוחת ערב </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ראיון עם פוליטיקו ובלומברג </t>
+  </si>
+  <si>
+    <t>אירוע של ECR בפרלמנט</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם חברת הפרלמנט הילדגרד בנטלה, מארחת האירוע בנושא "רפורמה ביבוא"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  תדרוך על הפרלמנט האירופי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם מארוס ספקוביץ'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  אירוע קבלת פנים וארוחת צהרים בבית השגרירה לבלגיה ולוקסמבורג</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  מפגש עם חבר/ת פרלמנט </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  אירוע  פרלמנט בנושא הרפורמה ביבוא</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ארוחת בוקר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  נסיעה לפרלמנט </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  יציאה לאירוע צהרים קבלת פנים
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם חבר הפרלמנט האירופי ויקטור נגרסקו</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> תדרוך עיתונות עם דוברת השגרירות  גב' פנטאי אלמו</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ארוחת בוקר במלון + צ'ק אאוט </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> מפגש עם בכירי הקהילה היהודית העסקית בהולנד </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה עם שר הכלכלה  Mr. Dirk Beljaarts</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ראיון לעיתון Elsevier Weekblad</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> נסיעה לראיון </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> נסיעה לארוחת צהריים </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ראיון לעיתון De Telegraaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> נסיעה למשרד הכלכלה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> נסיעה לאמסטרדם </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ארוחת צהריים פרטית</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> תדרוך עיתונות עם דוברת שגרירות  גב' פנטאי אלמו  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה עם נסיך הולנד  H.E. Prince Constantijn_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה בשגרירות האג + תדרוך </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> יציאה מבריסל לשגרירות ישראל בהאג </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  טיסה לישראל </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה עם מנכ"ל ING  Mr. Peter Jacobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ארוחת ערב פרטית </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ביקור מודרך במוזיאון השואה וברובע התרבות היהודי</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> נסיעה לשדה התעופה</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> יציאה מהמלון למשרדי KLM </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> התרעננות קצרה במלון </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> נסיעה לING </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> אירוע עסקי במלון Cl</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> נסיעה לרובע היהודי באמסטרדם </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה עם COO של KLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ארוחת צהריים עם משקיעים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  נחיתה בישראל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  וועדת שרים למינויים בחוץ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה פגישה מטה מול מטה עם משרד החוץ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ועדת השרים לקידום מעמד האישה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם Heather Johanson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  מטה מול מטה עם משרד החוץ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> סטטוס רפורמת מה שטוב לאירופה</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> אנואר סאב </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> טקס נטיעות באנדרטה העירונית לזכר חללי שבעה באוקטובר ומלחמת "חרבות ברזל" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  וועדת הפרס יום האחדות</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> דיון אצל רוה"מ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> אסף נחמיה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  טקס האזכרה הממלכתי ליוסף טרומפלדו וחבריו (לידיעה)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בת מצווה לבת של יאיר כץ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  חתונה לבן של יהורם לאונה חבר מרכז</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  משה בן שמעון מקיסריה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לפגישה עם שר החוץ של אתיופיה</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לוועדת שרים למילואים </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה עם שר החוץ של אתיופיה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ועדת שרים לעניין מערך המילואים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  חתונה של הבן של מאיר כהן מרמלה</t>
+  </si>
+  <si>
+    <t>חופשה מרוכזת</t>
+  </si>
+  <si>
+    <t>יום חופש חופשה מרוכזת</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ישיבת לוז </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לשגרירה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  מ"מ שגרירה ארה"ב בישראל  סטפני האלט , רפורמת התקנים </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לפגישה עם שר הכלכלה המקביל מאזרבייג'אן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  שר הכלכלה המקביל מאזרבייג'אן </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  רמי ויפית לוי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  טיוטת חוק פיקוח היצוא </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ישיבת הממשלה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פ.ע יוסי יעקב ויוני </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    פ.ע יוסי והשר אישי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישת עבודה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> בועז גנור </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ראיון פתחי וזמרי (מצולם)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ועידת הנגב בדימונה + ריאיון </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  נסיעה לברקן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  סיור אצל יוסי דגן</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> אצל ביטן עם שר האוצר בנושא הגנת הצרכן (משתתפים שר האוצר רמט+ כפיר בטאט)_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לוועדת שרים בנושא עליה וקליטה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  תורנות במליאה  עד לתום הישיבה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ניחום אבלים נזאר עראידה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ישיבת ממשלה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לסיור </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> מפגש פוליטי אצל חה"כ עפיף עבד </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> מועצת ירכא יחד עם חה"כ עפיף עבד </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה מקצועית במועצה אזורית עמק המעיינות </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> שי בן יעיש </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ועדת שרים לענייני עלייה וקליטה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  אלי כהן בנושא תרקומיא</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  מאיר בן שבת </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ברוך עייש </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  הכנה לכנס הגנת הצרכן  כותבת נאומים </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> נציג ממשלה ביום לאומי של יוון </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> תורנות במליאה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הצבעות תקציב במליאה  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> שיחת זום עם ניר ברקת וצוותו</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  אס"ח תאילנד </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  כנס יום הצרכן </t>
+  </si>
+  <si>
+    <t xml:space="preserve">דיון  חתימות </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ביקור בבת ים אצל החטופה אלמה אברהם</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Mr. Mirek Dusek  Managing Director  at the World Economic Forum (WEF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  משפחתו של החייל החטוף נמרוד כהן</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> השר ברקת + צחי וייספלד </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> זום בנושא קנאביס</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  נועם אמיר ערוץ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">נסיעה לתל אביב </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לדיון עם רוה"מ בנושא בינה מלאכותית בהון אנושי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  דיון אצל רוה"מ בנושא בינה מלאכותית להון אנושי בשירות המדינה </t>
+  </si>
+  <si>
+    <t>דיון אצל שר הביטחון</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פ.ע עם רון תומר </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  פגישה עם השרה מירי רגב  תקני מועצת השמאים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  דניאל ליפשיץ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה מקצועית עם השר אלקין  נושא החלטת ממשלה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הכנה לשר ההונגרי</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> הרמת כוסית לפסח משרד הכלכלה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  בת מצווה לבת של מתן ואפרת דיל </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> פגישה אישית עם השר ההונגרי </t>
   </si>
 </sst>
 </file>
@@ -1789,12 +3101,18 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="21" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2152,7 +3470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D470"/>
+  <dimension ref="A1:D974"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.58203125" style="1" customWidth="1"/>
@@ -8742,6 +10060,7062 @@
         <v>408</v>
       </c>
     </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A471" s="5">
+        <v>45658</v>
+      </c>
+      <c r="B471" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C471" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D471" s="7" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A472" s="5">
+        <v>45658</v>
+      </c>
+      <c r="B472" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="C472" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D472" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A473" s="5">
+        <v>45658</v>
+      </c>
+      <c r="B473" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C473" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D473" s="7" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A474" s="5">
+        <v>45658</v>
+      </c>
+      <c r="B474" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C474" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D474" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A475" s="5">
+        <v>45658</v>
+      </c>
+      <c r="B475" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C475" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D475" s="7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A476" s="5">
+        <v>45658</v>
+      </c>
+      <c r="B476" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C476" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D476" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A477" s="5">
+        <v>45659</v>
+      </c>
+      <c r="B477" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C477" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D477" s="7" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A478" s="5">
+        <v>45659</v>
+      </c>
+      <c r="B478" s="6">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="C478" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D478" s="7" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A479" s="5">
+        <v>45659</v>
+      </c>
+      <c r="B479" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C479" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D479" s="7" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A480" s="5">
+        <v>45659</v>
+      </c>
+      <c r="B480" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C480" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D480" s="7" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A481" s="5">
+        <v>45659</v>
+      </c>
+      <c r="B481" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C481" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D481" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A482" s="5">
+        <v>45659</v>
+      </c>
+      <c r="B482" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C482" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D482" s="7" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A483" s="5">
+        <v>45659</v>
+      </c>
+      <c r="B483" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C483" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="D483" s="7" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A484" s="5">
+        <v>45662</v>
+      </c>
+      <c r="B484" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C484" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D484" s="7" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A485" s="5">
+        <v>45662</v>
+      </c>
+      <c r="B485" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C485" s="6">
+        <v>0.53125</v>
+      </c>
+      <c r="D485" s="7" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A486" s="5">
+        <v>45662</v>
+      </c>
+      <c r="B486" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C486" s="6">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="D486" s="7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A487" s="5">
+        <v>45662</v>
+      </c>
+      <c r="B487" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C487" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D487" s="7" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A488" s="5">
+        <v>45662</v>
+      </c>
+      <c r="B488" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C488" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D488" s="7" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A489" s="5">
+        <v>45662</v>
+      </c>
+      <c r="B489" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="C489" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D489" s="7" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A490" s="5">
+        <v>45662</v>
+      </c>
+      <c r="B490" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C490" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D490" s="7" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A491" s="5">
+        <v>45662</v>
+      </c>
+      <c r="B491" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C491" s="6">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D491" s="7" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A492" s="5">
+        <v>45662</v>
+      </c>
+      <c r="B492" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C492" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D492" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A493" s="5">
+        <v>45662</v>
+      </c>
+      <c r="B493" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C493" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D493" s="7" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A494" s="5">
+        <v>45662</v>
+      </c>
+      <c r="B494" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C494" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D494" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A495" s="5">
+        <v>45663</v>
+      </c>
+      <c r="B495" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C495" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D495" s="7" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A496" s="5">
+        <v>45663</v>
+      </c>
+      <c r="B496" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C496" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D496" s="7" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A497" s="5">
+        <v>45663</v>
+      </c>
+      <c r="B497" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C497" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D497" s="7" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A498" s="5">
+        <v>45663</v>
+      </c>
+      <c r="B498" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="C498" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D498" s="7" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A499" s="5">
+        <v>45663</v>
+      </c>
+      <c r="B499" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C499" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D499" s="7" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A500" s="5">
+        <v>45663</v>
+      </c>
+      <c r="B500" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="C500" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D500" s="7" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A501" s="5">
+        <v>45663</v>
+      </c>
+      <c r="B501" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C501" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D501" s="7" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A502" s="5">
+        <v>45663</v>
+      </c>
+      <c r="B502" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C502" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D502" s="7" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A503" s="5">
+        <v>45663</v>
+      </c>
+      <c r="B503" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C503" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D503" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A504" s="5">
+        <v>45663</v>
+      </c>
+      <c r="B504" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C504" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D504" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A505" s="5">
+        <v>45664</v>
+      </c>
+      <c r="B505" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C505" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D505" s="7" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A506" s="5">
+        <v>45664</v>
+      </c>
+      <c r="B506" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C506" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D506" s="7" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A507" s="5">
+        <v>45664</v>
+      </c>
+      <c r="B507" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C507" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D507" s="7" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A508" s="5">
+        <v>45664</v>
+      </c>
+      <c r="B508" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C508" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D508" s="7" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A509" s="5">
+        <v>45664</v>
+      </c>
+      <c r="B509" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C509" s="6">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="D509" s="7" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A510" s="5">
+        <v>45664</v>
+      </c>
+      <c r="B510" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C510" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D510" s="7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A511" s="5">
+        <v>45664</v>
+      </c>
+      <c r="B511" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C511" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D511" s="7" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A512" s="5">
+        <v>45664</v>
+      </c>
+      <c r="B512" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C512" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D512" s="7" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A513" s="5">
+        <v>45664</v>
+      </c>
+      <c r="B513" s="6">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="C513" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D513" s="7" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A514" s="5">
+        <v>45665</v>
+      </c>
+      <c r="B514" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C514" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D514" s="7" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A515" s="5">
+        <v>45665</v>
+      </c>
+      <c r="B515" s="6">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="C515" s="6">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="D515" s="7" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A516" s="5">
+        <v>45665</v>
+      </c>
+      <c r="B516" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C516" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D516" s="7" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A517" s="5">
+        <v>45665</v>
+      </c>
+      <c r="B517" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C517" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D517" s="7" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A518" s="5">
+        <v>45665</v>
+      </c>
+      <c r="B518" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C518" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D518" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A519" s="5">
+        <v>45666</v>
+      </c>
+      <c r="B519" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C519" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D519" s="7" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A520" s="5">
+        <v>45666</v>
+      </c>
+      <c r="B520" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C520" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D520" s="7" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A521" s="5">
+        <v>45666</v>
+      </c>
+      <c r="B521" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C521" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D521" s="7" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A522" s="5">
+        <v>45666</v>
+      </c>
+      <c r="B522" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C522" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D522" s="7" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A523" s="5">
+        <v>45666</v>
+      </c>
+      <c r="B523" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C523" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D523" s="7" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A524" s="5">
+        <v>45666</v>
+      </c>
+      <c r="B524" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="C524" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="D524" s="7" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A525" s="5">
+        <v>45666</v>
+      </c>
+      <c r="B525" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C525" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="D525" s="7" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A526" s="5">
+        <v>45666</v>
+      </c>
+      <c r="B526" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C526" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D526" s="7" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A527" s="5">
+        <v>45666</v>
+      </c>
+      <c r="B527" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C527" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D527" s="7" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A528" s="5">
+        <v>45668</v>
+      </c>
+      <c r="B528" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C528" s="6">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D528" s="7" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A529" s="5">
+        <v>45669</v>
+      </c>
+      <c r="B529" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C529" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D529" s="7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A530" s="5">
+        <v>45669</v>
+      </c>
+      <c r="B530" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C530" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D530" s="7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A531" s="5">
+        <v>45669</v>
+      </c>
+      <c r="B531" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C531" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D531" s="7" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A532" s="5">
+        <v>45669</v>
+      </c>
+      <c r="B532" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C532" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D532" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A533" s="5">
+        <v>45669</v>
+      </c>
+      <c r="B533" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C533" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D533" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A534" s="5">
+        <v>45669</v>
+      </c>
+      <c r="B534" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C534" s="6">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="D534" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A535" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B535" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C535" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D535" s="7" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A536" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B536" s="6">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="C536" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D536" s="7" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A537" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B537" s="6">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="C537" s="6">
+        <v>0.84375</v>
+      </c>
+      <c r="D537" s="7" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A538" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B538" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C538" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D538" s="7" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A539" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B539" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C539" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D539" s="7" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A540" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B540" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C540" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D540" s="7" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A541" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B541" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C541" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D541" s="7" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A542" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B542" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C542" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D542" s="7" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A543" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B543" s="6">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="C543" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D543" s="7" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A544" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B544" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C544" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D544" s="7" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A545" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B545" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C545" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D545" s="7" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A546" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B546" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C546" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D546" s="7" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A547" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B547" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C547" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D547" s="7" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A548" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B548" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C548" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D548" s="7" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A549" s="5">
+        <v>45670</v>
+      </c>
+      <c r="B549" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C549" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D549" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A550" s="5">
+        <v>45671</v>
+      </c>
+      <c r="B550" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C550" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D550" s="7" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A551" s="5">
+        <v>45671</v>
+      </c>
+      <c r="B551" s="6">
+        <v>0.84375</v>
+      </c>
+      <c r="C551" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D551" s="7" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A552" s="5">
+        <v>45671</v>
+      </c>
+      <c r="B552" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C552" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D552" s="7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A553" s="5">
+        <v>45671</v>
+      </c>
+      <c r="B553" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C553" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D553" s="7" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A554" s="5">
+        <v>45671</v>
+      </c>
+      <c r="B554" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="C554" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="D554" s="7" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A555" s="5">
+        <v>45671</v>
+      </c>
+      <c r="B555" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C555" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D555" s="7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A556" s="5">
+        <v>45671</v>
+      </c>
+      <c r="B556" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C556" s="6">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D556" s="7" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A557" s="5">
+        <v>45672</v>
+      </c>
+      <c r="B557" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C557" s="6">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="D557" s="7" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A558" s="5">
+        <v>45672</v>
+      </c>
+      <c r="B558" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C558" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D558" s="7" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A559" s="5">
+        <v>45672</v>
+      </c>
+      <c r="B559" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C559" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D559" s="7" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A560" s="5">
+        <v>45672</v>
+      </c>
+      <c r="B560" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C560" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D560" s="7" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A561" s="5">
+        <v>45672</v>
+      </c>
+      <c r="B561" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C561" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D561" s="7" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A562" s="5">
+        <v>45672</v>
+      </c>
+      <c r="B562" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C562" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D562" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A563" s="5">
+        <v>45672</v>
+      </c>
+      <c r="B563" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="C563" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D563" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A564" s="5">
+        <v>45672</v>
+      </c>
+      <c r="B564" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C564" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="D564" s="7" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A565" s="5">
+        <v>45672</v>
+      </c>
+      <c r="B565" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C565" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D565" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A566" s="5">
+        <v>45673</v>
+      </c>
+      <c r="B566" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C566" s="6">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="D566" s="7" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A567" s="5">
+        <v>45673</v>
+      </c>
+      <c r="B567" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C567" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D567" s="7" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A568" s="5">
+        <v>45673</v>
+      </c>
+      <c r="B568" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C568" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D568" s="7" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A569" s="5">
+        <v>45673</v>
+      </c>
+      <c r="B569" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C569" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D569" s="7" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A570" s="5">
+        <v>45673</v>
+      </c>
+      <c r="B570" s="6">
+        <v>0.9375</v>
+      </c>
+      <c r="C570" s="6">
+        <v>0.96875</v>
+      </c>
+      <c r="D570" s="7" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A571" s="5">
+        <v>45673</v>
+      </c>
+      <c r="B571" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C571" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D571" s="7" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A572" s="5">
+        <v>45673</v>
+      </c>
+      <c r="B572" s="6">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="C572" s="6">
+        <v>0.90625</v>
+      </c>
+      <c r="D572" s="7" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A573" s="5">
+        <v>45676</v>
+      </c>
+      <c r="B573" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C573" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D573" s="7" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A574" s="5">
+        <v>45676</v>
+      </c>
+      <c r="B574" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C574" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D574" s="7" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A575" s="5">
+        <v>45676</v>
+      </c>
+      <c r="B575" s="6">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="C575" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D575" s="7" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A576" s="5">
+        <v>45676</v>
+      </c>
+      <c r="B576" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C576" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D576" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A577" s="5">
+        <v>45676</v>
+      </c>
+      <c r="B577" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C577" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="D577" s="7" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A578" s="5">
+        <v>45676</v>
+      </c>
+      <c r="B578" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C578" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D578" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A579" s="5">
+        <v>45676</v>
+      </c>
+      <c r="B579" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C579" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D579" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A580" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B580" s="6">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="C580" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D580" s="7" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A581" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B581" s="6">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="C581" s="6">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="D581" s="7" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A582" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B582" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C582" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D582" s="7" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A583" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B583" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C583" s="6">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D583" s="7" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A584" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B584" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C584" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D584" s="7" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A585" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B585" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C585" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D585" s="7" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A586" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B586" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C586" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D586" s="7" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A587" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B587" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C587" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D587" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A588" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B588" s="6">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C588" s="6">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D588" s="7" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A589" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B589" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C589" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D589" s="7" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A590" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B590" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C590" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D590" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A591" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B591" s="6">
+        <v>0</v>
+      </c>
+      <c r="C591" s="6">
+        <v>0</v>
+      </c>
+      <c r="D591" s="7" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A592" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B592" s="6">
+        <v>0.53125</v>
+      </c>
+      <c r="C592" s="6">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D592" s="7" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A593" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B593" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="C593" s="6">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="D593" s="7" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A594" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B594" s="6">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="C594" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D594" s="7" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A595" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B595" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C595" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D595" s="7" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A596" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B596" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C596" s="6">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D596" s="7" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A597" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B597" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C597" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D597" s="7" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A598" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B598" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C598" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D598" s="7" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A599" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B599" s="6">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="C599" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D599" s="7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A600" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B600" s="6">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="C600" s="6">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="D600" s="7" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A601" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B601" s="6">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="C601" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D601" s="7" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A602" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B602" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C602" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D602" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A603" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B603" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C603" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D603" s="7" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A604" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B604" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C604" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D604" s="7" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A605" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B605" s="6">
+        <v>0.20555555555555555</v>
+      </c>
+      <c r="C605" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D605" s="7" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A606" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B606" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C606" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D606" s="7" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A607" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B607" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C607" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D607" s="7" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A608" s="5">
+        <v>45678</v>
+      </c>
+      <c r="B608" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C608" s="6">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D608" s="7" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A609" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B609" s="6">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="C609" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D609" s="7" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A610" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B610" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C610" s="6">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="D610" s="7" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" ht="55.95" x14ac:dyDescent="0.3">
+      <c r="A611" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B611" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C611" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D611" s="8" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A612" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B612" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C612" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D612" s="7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A613" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B613" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C613" s="6">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D613" s="7" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A614" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B614" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="C614" s="6">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D614" s="7" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A615" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B615" s="6">
+        <v>0.90972222222222221</v>
+      </c>
+      <c r="C615" s="6">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="D615" s="7" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A616" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B616" s="6">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="C616" s="6">
+        <v>0.90972222222222221</v>
+      </c>
+      <c r="D616" s="7" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A617" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B617" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C617" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D617" s="7" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A618" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B618" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C618" s="6">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="D618" s="7" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A619" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B619" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C619" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D619" s="7" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A620" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B620" s="6">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C620" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D620" s="7" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A621" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B621" s="6">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="C621" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D621" s="7" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A622" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B622" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C622" s="6">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="D622" s="7" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A623" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B623" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C623" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D623" s="7" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A624" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B624" s="6">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="C624" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D624" s="7" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A625" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B625" s="6">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="C625" s="6">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="D625" s="7" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A626" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B626" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C626" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="D626" s="7" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A627" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B627" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C627" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D627" s="7" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A628" s="5">
+        <v>45679</v>
+      </c>
+      <c r="B628" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C628" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D628" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A629" s="5">
+        <v>45680</v>
+      </c>
+      <c r="B629" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C629" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D629" s="7" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A630" s="5">
+        <v>45680</v>
+      </c>
+      <c r="B630" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C630" s="6">
+        <v>0.71875</v>
+      </c>
+      <c r="D630" s="7" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A631" s="5">
+        <v>45680</v>
+      </c>
+      <c r="B631" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="C631" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D631" s="7" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A632" s="5">
+        <v>45680</v>
+      </c>
+      <c r="B632" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C632" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="D632" s="7" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A633" s="5">
+        <v>45683</v>
+      </c>
+      <c r="B633" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C633" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D633" s="7" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A634" s="5">
+        <v>45683</v>
+      </c>
+      <c r="B634" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C634" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D634" s="7" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A635" s="5">
+        <v>45683</v>
+      </c>
+      <c r="B635" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C635" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D635" s="7" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A636" s="5">
+        <v>45683</v>
+      </c>
+      <c r="B636" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C636" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D636" s="7" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A637" s="5">
+        <v>45683</v>
+      </c>
+      <c r="B637" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C637" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D637" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A638" s="5">
+        <v>45683</v>
+      </c>
+      <c r="B638" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C638" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D638" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A639" s="5">
+        <v>45683</v>
+      </c>
+      <c r="B639" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C639" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D639" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A640" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B640" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C640" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D640" s="7" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A641" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B641" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="C641" s="6">
+        <v>0.90277777777777779</v>
+      </c>
+      <c r="D641" s="7" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A642" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B642" s="6">
+        <v>0.90277777777777779</v>
+      </c>
+      <c r="C642" s="6">
+        <v>0.92361111111111116</v>
+      </c>
+      <c r="D642" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A643" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B643" s="6">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C643" s="6">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="D643" s="7" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A644" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B644" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C644" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D644" s="7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A645" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B645" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C645" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D645" s="7" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A646" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B646" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C646" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D646" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A647" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B647" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C647" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D647" s="7" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A648" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B648" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="C648" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D648" s="7" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A649" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B649" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C649" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D649" s="7" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A650" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B650" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="C650" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D650" s="7" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A651" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B651" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C651" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D651" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A652" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B652" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C652" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D652" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A653" s="5">
+        <v>45684</v>
+      </c>
+      <c r="B653" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C653" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D653" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A654" s="5">
+        <v>45685</v>
+      </c>
+      <c r="B654" s="6">
+        <v>0.53125</v>
+      </c>
+      <c r="C654" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D654" s="7" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A655" s="5">
+        <v>45685</v>
+      </c>
+      <c r="B655" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C655" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D655" s="7" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A656" s="5">
+        <v>45685</v>
+      </c>
+      <c r="B656" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C656" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D656" s="7" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A657" s="5">
+        <v>45685</v>
+      </c>
+      <c r="B657" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C657" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D657" s="7" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A658" s="5">
+        <v>45685</v>
+      </c>
+      <c r="B658" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C658" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D658" s="7" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A659" s="5">
+        <v>45685</v>
+      </c>
+      <c r="B659" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C659" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D659" s="7" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A660" s="5">
+        <v>45685</v>
+      </c>
+      <c r="B660" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="C660" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D660" s="7" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A661" s="5">
+        <v>45685</v>
+      </c>
+      <c r="B661" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C661" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D661" s="7" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A662" s="5">
+        <v>45685</v>
+      </c>
+      <c r="B662" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C662" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D662" s="7" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A663" s="5">
+        <v>45686</v>
+      </c>
+      <c r="B663" s="6">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="C663" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D663" s="7" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A664" s="5">
+        <v>45686</v>
+      </c>
+      <c r="B664" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C664" s="6">
+        <v>0.53125</v>
+      </c>
+      <c r="D664" s="7" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A665" s="5">
+        <v>45686</v>
+      </c>
+      <c r="B665" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C665" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D665" s="7" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A666" s="5">
+        <v>45686</v>
+      </c>
+      <c r="B666" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C666" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D666" s="7" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A667" s="5">
+        <v>45686</v>
+      </c>
+      <c r="B667" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C667" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D667" s="7" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A668" s="5">
+        <v>45686</v>
+      </c>
+      <c r="B668" s="6">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="C668" s="6">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="D668" s="7" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A669" s="5">
+        <v>45686</v>
+      </c>
+      <c r="B669" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C669" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D669" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A670" s="5">
+        <v>45687</v>
+      </c>
+      <c r="B670" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C670" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D670" s="7" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A671" s="5">
+        <v>45687</v>
+      </c>
+      <c r="B671" s="6">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="C671" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D671" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A672" s="5">
+        <v>45687</v>
+      </c>
+      <c r="B672" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C672" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D672" s="7" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A673" s="5">
+        <v>45687</v>
+      </c>
+      <c r="B673" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C673" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D673" s="7" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A674" s="5">
+        <v>45687</v>
+      </c>
+      <c r="B674" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C674" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D674" s="7" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A675" s="5">
+        <v>45687</v>
+      </c>
+      <c r="B675" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C675" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D675" s="7" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A676" s="5">
+        <v>45687</v>
+      </c>
+      <c r="B676" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C676" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D676" s="7" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A677" s="5">
+        <v>45687</v>
+      </c>
+      <c r="B677" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C677" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D677" s="7" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A678" s="5">
+        <v>45690</v>
+      </c>
+      <c r="B678" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C678" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D678" s="7" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A679" s="5">
+        <v>45690</v>
+      </c>
+      <c r="B679" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C679" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D679" s="7" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A680" s="5">
+        <v>45690</v>
+      </c>
+      <c r="B680" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C680" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D680" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A681" s="5">
+        <v>45690</v>
+      </c>
+      <c r="B681" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C681" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D681" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A682" s="5">
+        <v>45690</v>
+      </c>
+      <c r="B682" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C682" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D682" s="7" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A683" s="5">
+        <v>45690</v>
+      </c>
+      <c r="B683" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C683" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D683" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A684" s="5">
+        <v>45691</v>
+      </c>
+      <c r="B684" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C684" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D684" s="7" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A685" s="5">
+        <v>45691</v>
+      </c>
+      <c r="B685" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C685" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D685" s="7" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A686" s="5">
+        <v>45691</v>
+      </c>
+      <c r="B686" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="C686" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D686" s="7" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A687" s="5">
+        <v>45691</v>
+      </c>
+      <c r="B687" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C687" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D687" s="7" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A688" s="5">
+        <v>45691</v>
+      </c>
+      <c r="B688" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C688" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D688" s="7" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A689" s="5">
+        <v>45691</v>
+      </c>
+      <c r="B689" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C689" s="6">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="D689" s="7" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A690" s="5">
+        <v>45691</v>
+      </c>
+      <c r="B690" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C690" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D690" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A691" s="5">
+        <v>45692</v>
+      </c>
+      <c r="B691" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C691" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D691" s="7" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A692" s="5">
+        <v>45692</v>
+      </c>
+      <c r="B692" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C692" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D692" s="7" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A693" s="5">
+        <v>45692</v>
+      </c>
+      <c r="B693" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C693" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D693" s="7" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A694" s="5">
+        <v>45692</v>
+      </c>
+      <c r="B694" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C694" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D694" s="7" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A695" s="5">
+        <v>45692</v>
+      </c>
+      <c r="B695" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C695" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D695" s="7" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A696" s="5">
+        <v>45693</v>
+      </c>
+      <c r="B696" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C696" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D696" s="7" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A697" s="5">
+        <v>45693</v>
+      </c>
+      <c r="B697" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C697" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D697" s="7" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A698" s="5">
+        <v>45693</v>
+      </c>
+      <c r="B698" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C698" s="6">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D698" s="7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A699" s="5">
+        <v>45693</v>
+      </c>
+      <c r="B699" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C699" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D699" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A700" s="5">
+        <v>45693</v>
+      </c>
+      <c r="B700" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C700" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D700" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A701" s="5">
+        <v>45694</v>
+      </c>
+      <c r="B701" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C701" s="6">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="D701" s="7" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A702" s="5">
+        <v>45694</v>
+      </c>
+      <c r="B702" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C702" s="6">
+        <v>0.71875</v>
+      </c>
+      <c r="D702" s="7" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A703" s="5">
+        <v>45694</v>
+      </c>
+      <c r="B703" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C703" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D703" s="7" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A704" s="5">
+        <v>45694</v>
+      </c>
+      <c r="B704" s="6">
+        <v>0.71875</v>
+      </c>
+      <c r="C704" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D704" s="7" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A705" s="5">
+        <v>45694</v>
+      </c>
+      <c r="B705" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C705" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D705" s="7" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A706" s="5">
+        <v>45694</v>
+      </c>
+      <c r="B706" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C706" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D706" s="7" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A707" s="5">
+        <v>45694</v>
+      </c>
+      <c r="B707" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C707" s="6">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="D707" s="7" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A708" s="5">
+        <v>45697</v>
+      </c>
+      <c r="B708" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C708" s="6">
+        <v>0.78125</v>
+      </c>
+      <c r="D708" s="7" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A709" s="5">
+        <v>45697</v>
+      </c>
+      <c r="B709" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C709" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D709" s="7" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A710" s="5">
+        <v>45697</v>
+      </c>
+      <c r="B710" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="C710" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D710" s="7" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A711" s="5">
+        <v>45697</v>
+      </c>
+      <c r="B711" s="6">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="C711" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D711" s="7" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A712" s="5">
+        <v>45697</v>
+      </c>
+      <c r="B712" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C712" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D712" s="7" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A713" s="5">
+        <v>45698</v>
+      </c>
+      <c r="B713" s="6">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C713" s="6">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D713" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A714" s="5">
+        <v>45698</v>
+      </c>
+      <c r="B714" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C714" s="6">
+        <v>0.71875</v>
+      </c>
+      <c r="D714" s="7" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A715" s="5">
+        <v>45698</v>
+      </c>
+      <c r="B715" s="6">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="C715" s="6">
+        <v>0.96875</v>
+      </c>
+      <c r="D715" s="7" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A716" s="5">
+        <v>45698</v>
+      </c>
+      <c r="B716" s="6">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C716" s="6">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="D716" s="7" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A717" s="5">
+        <v>45698</v>
+      </c>
+      <c r="B717" s="6">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="C717" s="6">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D717" s="7" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A718" s="5">
+        <v>45698</v>
+      </c>
+      <c r="B718" s="6">
+        <v>0</v>
+      </c>
+      <c r="C718" s="6">
+        <v>0</v>
+      </c>
+      <c r="D718" s="7" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A719" s="5">
+        <v>45698</v>
+      </c>
+      <c r="B719" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C719" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D719" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="720" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A720" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B720" s="6">
+        <v>0.84722222222222221</v>
+      </c>
+      <c r="C720" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D720" s="7" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A721" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B721" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="C721" s="6">
+        <v>0.84722222222222221</v>
+      </c>
+      <c r="D721" s="7" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="722" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A722" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B722" s="6">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="C722" s="6">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="D722" s="7" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="723" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A723" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B723" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C723" s="6">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="D723" s="7" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="724" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A724" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B724" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C724" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D724" s="7" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="725" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A725" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B725" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C725" s="6">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D725" s="7" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A726" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B726" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C726" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D726" s="7" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A727" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B727" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="C727" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D727" s="7" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A728" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B728" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="C728" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D728" s="7" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A729" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B729" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C729" s="6">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="D729" s="7" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="730" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A730" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B730" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C730" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D730" s="7" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="731" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A731" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B731" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C731" s="6">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="D731" s="7" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="732" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A732" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B732" s="6">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C732" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D732" s="7" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="733" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A733" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B733" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C733" s="6">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="D733" s="7" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="734" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A734" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B734" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C734" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D734" s="7" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="735" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A735" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B735" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C735" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D735" s="7" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="736" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A736" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B736" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C736" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D736" s="7" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="737" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A737" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B737" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C737" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="D737" s="7" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="738" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A738" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B738" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C738" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D738" s="7" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="739" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A739" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B739" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C739" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D739" s="7" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="740" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A740" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B740" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="C740" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D740" s="7" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="741" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A741" s="5">
+        <v>45699</v>
+      </c>
+      <c r="B741" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C741" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D741" s="7" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="742" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A742" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B742" s="6">
+        <v>0.84375</v>
+      </c>
+      <c r="C742" s="6">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="D742" s="7" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="743" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A743" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B743" s="6">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="C743" s="6">
+        <v>0.84375</v>
+      </c>
+      <c r="D743" s="7" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="744" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A744" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B744" s="6">
+        <v>0.78125</v>
+      </c>
+      <c r="C744" s="6">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D744" s="7" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="745" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A745" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B745" s="6">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="C745" s="6">
+        <v>0.78125</v>
+      </c>
+      <c r="D745" s="7" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="746" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A746" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B746" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C746" s="6">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="D746" s="7" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="747" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A747" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B747" s="6">
+        <v>0.71875</v>
+      </c>
+      <c r="C747" s="6">
+        <v>0.72569444444444442</v>
+      </c>
+      <c r="D747" s="7" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="748" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A748" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B748" s="6">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="C748" s="6">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="D748" s="7" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="749" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A749" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B749" s="6">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="C749" s="6">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="D749" s="7" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="750" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A750" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B750" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C750" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D750" s="7" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="751" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A751" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B751" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C751" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D751" s="7" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="752" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A752" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B752" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="C752" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D752" s="7" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="753" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A753" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B753" s="6">
+        <v>0.53125</v>
+      </c>
+      <c r="C753" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D753" s="7" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="754" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A754" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B754" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C754" s="6">
+        <v>0.53125</v>
+      </c>
+      <c r="D754" s="7" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="755" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A755" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B755" s="6">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="C755" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D755" s="7" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="756" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A756" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B756" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C756" s="6">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D756" s="7" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="757" spans="1:4" ht="55.95" x14ac:dyDescent="0.3">
+      <c r="A757" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B757" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C757" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D757" s="8" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="758" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A758" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B758" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C758" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D758" s="7" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="759" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A759" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B759" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C759" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D759" s="7" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="760" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A760" s="5">
+        <v>45700</v>
+      </c>
+      <c r="B760" s="6">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C760" s="6">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="D760" s="7" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="761" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A761" s="5">
+        <v>45701</v>
+      </c>
+      <c r="B761" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C761" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D761" s="7" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="762" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A762" s="5">
+        <v>45701</v>
+      </c>
+      <c r="B762" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="C762" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D762" s="7" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="763" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A763" s="5">
+        <v>45701</v>
+      </c>
+      <c r="B763" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C763" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="D763" s="7" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="764" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A764" s="5">
+        <v>45701</v>
+      </c>
+      <c r="B764" s="6">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="C764" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D764" s="7" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="765" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A765" s="5">
+        <v>45701</v>
+      </c>
+      <c r="B765" s="6">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="C765" s="6">
+        <v>0.72569444444444442</v>
+      </c>
+      <c r="D765" s="7" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="766" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A766" s="5">
+        <v>45703</v>
+      </c>
+      <c r="B766" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C766" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D766" s="7" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="767" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A767" s="5">
+        <v>45704</v>
+      </c>
+      <c r="B767" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C767" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D767" s="7" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="768" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A768" s="5">
+        <v>45704</v>
+      </c>
+      <c r="B768" s="6">
+        <v>0.53125</v>
+      </c>
+      <c r="C768" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D768" s="7" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="769" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A769" s="5">
+        <v>45704</v>
+      </c>
+      <c r="B769" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C769" s="6">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D769" s="7" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="770" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A770" s="5">
+        <v>45704</v>
+      </c>
+      <c r="B770" s="6">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="C770" s="6">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="D770" s="7" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="771" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A771" s="5">
+        <v>45704</v>
+      </c>
+      <c r="B771" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C771" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="D771" s="7" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="772" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A772" s="5">
+        <v>45704</v>
+      </c>
+      <c r="B772" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C772" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D772" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="773" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A773" s="5">
+        <v>45704</v>
+      </c>
+      <c r="B773" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C773" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D773" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="774" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A774" s="5">
+        <v>45704</v>
+      </c>
+      <c r="B774" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C774" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D774" s="7" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="775" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A775" s="5">
+        <v>45705</v>
+      </c>
+      <c r="B775" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="C775" s="6">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="D775" s="7" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="776" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A776" s="5">
+        <v>45705</v>
+      </c>
+      <c r="B776" s="6">
+        <v>0.61805555555555558</v>
+      </c>
+      <c r="C776" s="6">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D776" s="7" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="777" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A777" s="5">
+        <v>45705</v>
+      </c>
+      <c r="B777" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C777" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D777" s="7" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A778" s="5">
+        <v>45705</v>
+      </c>
+      <c r="B778" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C778" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D778" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A779" s="5">
+        <v>45706</v>
+      </c>
+      <c r="B779" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C779" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D779" s="7" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A780" s="5">
+        <v>45706</v>
+      </c>
+      <c r="B780" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C780" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D780" s="7" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A781" s="5">
+        <v>45706</v>
+      </c>
+      <c r="B781" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C781" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D781" s="7" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A782" s="5">
+        <v>45706</v>
+      </c>
+      <c r="B782" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C782" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D782" s="7" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A783" s="5">
+        <v>45706</v>
+      </c>
+      <c r="B783" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C783" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D783" s="7" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A784" s="5">
+        <v>45706</v>
+      </c>
+      <c r="B784" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C784" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D784" s="7" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A785" s="5">
+        <v>45706</v>
+      </c>
+      <c r="B785" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C785" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D785" s="7" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A786" s="5">
+        <v>45707</v>
+      </c>
+      <c r="B786" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C786" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D786" s="7" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A787" s="5">
+        <v>45707</v>
+      </c>
+      <c r="B787" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C787" s="6">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D787" s="7" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A788" s="5">
+        <v>45707</v>
+      </c>
+      <c r="B788" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C788" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D788" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A789" s="5">
+        <v>45708</v>
+      </c>
+      <c r="B789" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C789" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D789" s="7" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A790" s="5">
+        <v>45708</v>
+      </c>
+      <c r="B790" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C790" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D790" s="7" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A791" s="5">
+        <v>45708</v>
+      </c>
+      <c r="B791" s="6">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="C791" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D791" s="7" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A792" s="5">
+        <v>45711</v>
+      </c>
+      <c r="B792" s="6">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="C792" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="D792" s="7" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A793" s="5">
+        <v>45711</v>
+      </c>
+      <c r="B793" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C793" s="6">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="D793" s="7" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A794" s="5">
+        <v>45711</v>
+      </c>
+      <c r="B794" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C794" s="6">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D794" s="7" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A795" s="5">
+        <v>45711</v>
+      </c>
+      <c r="B795" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C795" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D795" s="7" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A796" s="5">
+        <v>45711</v>
+      </c>
+      <c r="B796" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C796" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D796" s="7" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A797" s="5">
+        <v>45711</v>
+      </c>
+      <c r="B797" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C797" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D797" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A798" s="5">
+        <v>45711</v>
+      </c>
+      <c r="B798" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C798" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D798" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A799" s="5">
+        <v>45711</v>
+      </c>
+      <c r="B799" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C799" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D799" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A800" s="5">
+        <v>45712</v>
+      </c>
+      <c r="B800" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C800" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D800" s="7" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A801" s="5">
+        <v>45712</v>
+      </c>
+      <c r="B801" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C801" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D801" s="7" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A802" s="5">
+        <v>45712</v>
+      </c>
+      <c r="B802" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C802" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D802" s="7" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A803" s="5">
+        <v>45712</v>
+      </c>
+      <c r="B803" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="C803" s="6">
+        <v>0.71875</v>
+      </c>
+      <c r="D803" s="7" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A804" s="5">
+        <v>45712</v>
+      </c>
+      <c r="B804" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C804" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D804" s="7" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A805" s="5">
+        <v>45712</v>
+      </c>
+      <c r="B805" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C805" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D805" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A806" s="5">
+        <v>45712</v>
+      </c>
+      <c r="B806" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C806" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D806" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A807" s="5">
+        <v>45713</v>
+      </c>
+      <c r="B807" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="C807" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D807" s="7" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A808" s="5">
+        <v>45713</v>
+      </c>
+      <c r="B808" s="6">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="C808" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D808" s="7" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A809" s="5">
+        <v>45713</v>
+      </c>
+      <c r="B809" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C809" s="6">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="D809" s="7" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A810" s="5">
+        <v>45713</v>
+      </c>
+      <c r="B810" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C810" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D810" s="7" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A811" s="5">
+        <v>45713</v>
+      </c>
+      <c r="B811" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C811" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D811" s="7" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A812" s="5">
+        <v>45713</v>
+      </c>
+      <c r="B812" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C812" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D812" s="7" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A813" s="5">
+        <v>45713</v>
+      </c>
+      <c r="B813" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C813" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D813" s="7" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A814" s="5">
+        <v>45713</v>
+      </c>
+      <c r="B814" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C814" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D814" s="7" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A815" s="5">
+        <v>45714</v>
+      </c>
+      <c r="B815" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C815" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D815" s="7" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A816" s="5">
+        <v>45714</v>
+      </c>
+      <c r="B816" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="C816" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D816" s="7" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A817" s="5">
+        <v>45714</v>
+      </c>
+      <c r="B817" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C817" s="6">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D817" s="7" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A818" s="5">
+        <v>45714</v>
+      </c>
+      <c r="B818" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C818" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D818" s="7" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A819" s="5">
+        <v>45714</v>
+      </c>
+      <c r="B819" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C819" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D819" s="7" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A820" s="5">
+        <v>45714</v>
+      </c>
+      <c r="B820" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C820" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D820" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A821" s="5">
+        <v>45715</v>
+      </c>
+      <c r="B821" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C821" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D821" s="7" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A822" s="5">
+        <v>45715</v>
+      </c>
+      <c r="B822" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C822" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D822" s="7" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A823" s="5">
+        <v>45715</v>
+      </c>
+      <c r="B823" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C823" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D823" s="7" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A824" s="5">
+        <v>45715</v>
+      </c>
+      <c r="B824" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C824" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D824" s="7" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A825" s="5">
+        <v>45715</v>
+      </c>
+      <c r="B825" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="C825" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D825" s="7" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A826" s="5">
+        <v>45718</v>
+      </c>
+      <c r="B826" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C826" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D826" s="7" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A827" s="5">
+        <v>45718</v>
+      </c>
+      <c r="B827" s="6">
+        <v>0.83680555555555558</v>
+      </c>
+      <c r="C827" s="6">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D827" s="7" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A828" s="5">
+        <v>45718</v>
+      </c>
+      <c r="B828" s="6">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C828" s="6">
+        <v>0.9375</v>
+      </c>
+      <c r="D828" s="7" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A829" s="5">
+        <v>45718</v>
+      </c>
+      <c r="B829" s="6">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="C829" s="6">
+        <v>0.83680555555555558</v>
+      </c>
+      <c r="D829" s="7" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A830" s="5">
+        <v>45718</v>
+      </c>
+      <c r="B830" s="6">
+        <v>0</v>
+      </c>
+      <c r="C830" s="6">
+        <v>0</v>
+      </c>
+      <c r="D830" s="7" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A831" s="5">
+        <v>45718</v>
+      </c>
+      <c r="B831" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C831" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D831" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A832" s="5">
+        <v>45718</v>
+      </c>
+      <c r="B832" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C832" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D832" s="7" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A833" s="5">
+        <v>45719</v>
+      </c>
+      <c r="B833" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C833" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D833" s="7" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A834" s="5">
+        <v>45719</v>
+      </c>
+      <c r="B834" s="6">
+        <v>0</v>
+      </c>
+      <c r="C834" s="6">
+        <v>0</v>
+      </c>
+      <c r="D834" s="7" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A835" s="5">
+        <v>45719</v>
+      </c>
+      <c r="B835" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C835" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D835" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A836" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B836" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C836" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="D836" s="7" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A837" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B837" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C837" s="6">
+        <v>0.71875</v>
+      </c>
+      <c r="D837" s="7" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A838" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B838" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C838" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="D838" s="7" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A839" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B839" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="C839" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D839" s="7" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A840" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B840" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C840" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D840" s="7" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A841" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B841" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C841" s="6">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="D841" s="7" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A842" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B842" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C842" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D842" s="7" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A843" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B843" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="C843" s="6">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="D843" s="7" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A844" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B844" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C844" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D844" s="7" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A845" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B845" s="6">
+        <v>0.3125</v>
+      </c>
+      <c r="C845" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D845" s="7" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A846" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B846" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C846" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D846" s="7" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4" ht="42" x14ac:dyDescent="0.3">
+      <c r="A847" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B847" s="6">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="C847" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D847" s="8" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A848" s="5">
+        <v>45720</v>
+      </c>
+      <c r="B848" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C848" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D848" s="7" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A849" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B849" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C849" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D849" s="7" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A850" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B850" s="6">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="C850" s="6">
+        <v>0.3125</v>
+      </c>
+      <c r="D850" s="7" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A851" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B851" s="6">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="C851" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="D851" s="7" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A852" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B852" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C852" s="6">
+        <v>0.71875</v>
+      </c>
+      <c r="D852" s="7" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="853" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A853" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B853" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C853" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D853" s="7" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A854" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B854" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C854" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D854" s="7" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="855" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A855" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B855" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C855" s="6">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D855" s="7" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A856" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B856" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C856" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D856" s="7" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="857" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A857" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B857" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C857" s="6">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D857" s="7" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A858" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B858" s="6">
+        <v>0.71875</v>
+      </c>
+      <c r="C858" s="6">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="D858" s="7" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A859" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B859" s="6">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="C859" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="D859" s="7" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A860" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B860" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C860" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D860" s="7" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="861" spans="1:4" ht="42" x14ac:dyDescent="0.3">
+      <c r="A861" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B861" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C861" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D861" s="8" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A862" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B862" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C862" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D862" s="7" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="863" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A863" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B863" s="6">
+        <v>0.3125</v>
+      </c>
+      <c r="C863" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D863" s="7" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A864" s="5">
+        <v>45721</v>
+      </c>
+      <c r="B864" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C864" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D864" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A865" s="5">
+        <v>45722</v>
+      </c>
+      <c r="B865" s="6">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C865" s="6">
+        <v>0.12152777777777778</v>
+      </c>
+      <c r="D865" s="7" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A866" s="5">
+        <v>45722</v>
+      </c>
+      <c r="B866" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C866" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D866" s="7" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A867" s="5">
+        <v>45722</v>
+      </c>
+      <c r="B867" s="6">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="C867" s="6">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="D867" s="7" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A868" s="5">
+        <v>45722</v>
+      </c>
+      <c r="B868" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C868" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D868" s="7" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A869" s="5">
+        <v>45722</v>
+      </c>
+      <c r="B869" s="6">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="C869" s="6">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D869" s="7" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A870" s="5">
+        <v>45722</v>
+      </c>
+      <c r="B870" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C870" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D870" s="7" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A871" s="5">
+        <v>45722</v>
+      </c>
+      <c r="B871" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C871" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="D871" s="7" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="872" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A872" s="5">
+        <v>45722</v>
+      </c>
+      <c r="B872" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="C872" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D872" s="7" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A873" s="5">
+        <v>45722</v>
+      </c>
+      <c r="B873" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="C873" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D873" s="7" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A874" s="5">
+        <v>45722</v>
+      </c>
+      <c r="B874" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C874" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D874" s="7" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A875" s="5">
+        <v>45722</v>
+      </c>
+      <c r="B875" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C875" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D875" s="7" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A876" s="5">
+        <v>45722</v>
+      </c>
+      <c r="B876" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C876" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D876" s="7" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A877" s="5">
+        <v>45723</v>
+      </c>
+      <c r="B877" s="6">
+        <v>0.12152777777777778</v>
+      </c>
+      <c r="C877" s="6">
+        <v>0.16319444444444445</v>
+      </c>
+      <c r="D877" s="7" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A878" s="5">
+        <v>45725</v>
+      </c>
+      <c r="B878" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C878" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D878" s="7" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="879" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A879" s="5">
+        <v>45725</v>
+      </c>
+      <c r="B879" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C879" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D879" s="7" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A880" s="5">
+        <v>45725</v>
+      </c>
+      <c r="B880" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="C880" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D880" s="7" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A881" s="5">
+        <v>45725</v>
+      </c>
+      <c r="B881" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C881" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D881" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="882" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A882" s="5">
+        <v>45725</v>
+      </c>
+      <c r="B882" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C882" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D882" s="7" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="883" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A883" s="5">
+        <v>45725</v>
+      </c>
+      <c r="B883" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C883" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D883" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A884" s="5">
+        <v>45725</v>
+      </c>
+      <c r="B884" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C884" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D884" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A885" s="5">
+        <v>45725</v>
+      </c>
+      <c r="B885" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C885" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D885" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="886" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A886" s="5">
+        <v>45726</v>
+      </c>
+      <c r="B886" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C886" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D886" s="7" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="887" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A887" s="5">
+        <v>45726</v>
+      </c>
+      <c r="B887" s="6">
+        <v>0.71875</v>
+      </c>
+      <c r="C887" s="6">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="D887" s="7" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="888" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A888" s="5">
+        <v>45726</v>
+      </c>
+      <c r="B888" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C888" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D888" s="7" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="889" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A889" s="5">
+        <v>45726</v>
+      </c>
+      <c r="B889" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C889" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D889" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="890" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A890" s="5">
+        <v>45726</v>
+      </c>
+      <c r="B890" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C890" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D890" s="7" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="891" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A891" s="5">
+        <v>45726</v>
+      </c>
+      <c r="B891" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C891" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D891" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A892" s="5">
+        <v>45727</v>
+      </c>
+      <c r="B892" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="C892" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D892" s="7" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A893" s="5">
+        <v>45727</v>
+      </c>
+      <c r="B893" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C893" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D893" s="7" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A894" s="5">
+        <v>45727</v>
+      </c>
+      <c r="B894" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C894" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D894" s="7" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="895" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A895" s="5">
+        <v>45727</v>
+      </c>
+      <c r="B895" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C895" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D895" s="7" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="896" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A896" s="5">
+        <v>45727</v>
+      </c>
+      <c r="B896" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="C896" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D896" s="7" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A897" s="5">
+        <v>45727</v>
+      </c>
+      <c r="B897" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C897" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D897" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="898" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A898" s="5">
+        <v>45728</v>
+      </c>
+      <c r="B898" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C898" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D898" s="7" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="899" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A899" s="5">
+        <v>45728</v>
+      </c>
+      <c r="B899" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C899" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D899" s="7" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="900" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A900" s="5">
+        <v>45728</v>
+      </c>
+      <c r="B900" s="6">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C900" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D900" s="7" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="901" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A901" s="5">
+        <v>45728</v>
+      </c>
+      <c r="B901" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="C901" s="6">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="D901" s="7" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="902" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A902" s="5">
+        <v>45728</v>
+      </c>
+      <c r="B902" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C902" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D902" s="7" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="903" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A903" s="5">
+        <v>45728</v>
+      </c>
+      <c r="B903" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C903" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D903" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="904" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A904" s="5">
+        <v>45732</v>
+      </c>
+      <c r="B904" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C904" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D904" s="7" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="905" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A905" s="5">
+        <v>45732</v>
+      </c>
+      <c r="B905" s="6">
+        <v>0.3125</v>
+      </c>
+      <c r="C905" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D905" s="7" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="906" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A906" s="5">
+        <v>45732</v>
+      </c>
+      <c r="B906" s="6">
+        <v>0</v>
+      </c>
+      <c r="C906" s="6">
+        <v>0</v>
+      </c>
+      <c r="D906" s="7" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="907" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A907" s="5">
+        <v>45733</v>
+      </c>
+      <c r="B907" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C907" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D907" s="7" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="908" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A908" s="5">
+        <v>45733</v>
+      </c>
+      <c r="B908" s="6">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="C908" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D908" s="7" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="909" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A909" s="5">
+        <v>45733</v>
+      </c>
+      <c r="B909" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C909" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D909" s="7" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="910" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A910" s="5">
+        <v>45733</v>
+      </c>
+      <c r="B910" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="C910" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D910" s="7" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="911" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A911" s="5">
+        <v>45733</v>
+      </c>
+      <c r="B911" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C911" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D911" s="7" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="912" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A912" s="5">
+        <v>45733</v>
+      </c>
+      <c r="B912" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C912" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D912" s="7" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="913" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A913" s="5">
+        <v>45733</v>
+      </c>
+      <c r="B913" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C913" s="6">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="D913" s="7" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="914" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A914" s="5">
+        <v>45733</v>
+      </c>
+      <c r="B914" s="6">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C914" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D914" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="915" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A915" s="5">
+        <v>45733</v>
+      </c>
+      <c r="B915" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C915" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D915" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="916" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A916" s="5">
+        <v>45734</v>
+      </c>
+      <c r="B916" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="C916" s="6">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D916" s="7" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="917" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A917" s="5">
+        <v>45734</v>
+      </c>
+      <c r="B917" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C917" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D917" s="7" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="918" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A918" s="5">
+        <v>45734</v>
+      </c>
+      <c r="B918" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C918" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D918" s="7" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="919" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A919" s="5">
+        <v>45734</v>
+      </c>
+      <c r="B919" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C919" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D919" s="7" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="920" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A920" s="5">
+        <v>45734</v>
+      </c>
+      <c r="B920" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C920" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="D920" s="7" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="921" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A921" s="5">
+        <v>45734</v>
+      </c>
+      <c r="B921" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C921" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D921" s="7" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="922" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A922" s="5">
+        <v>45734</v>
+      </c>
+      <c r="B922" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C922" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D922" s="7" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="923" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A923" s="5">
+        <v>45734</v>
+      </c>
+      <c r="B923" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C923" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D923" s="7" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="924" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A924" s="5">
+        <v>45734</v>
+      </c>
+      <c r="B924" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C924" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D924" s="7" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="925" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A925" s="5">
+        <v>45734</v>
+      </c>
+      <c r="B925" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C925" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D925" s="7" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="926" spans="1:4" ht="55.95" x14ac:dyDescent="0.3">
+      <c r="A926" s="5">
+        <v>45735</v>
+      </c>
+      <c r="B926" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C926" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D926" s="8" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="927" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A927" s="5">
+        <v>45735</v>
+      </c>
+      <c r="B927" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="C927" s="6">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D927" s="7" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="928" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A928" s="5">
+        <v>45735</v>
+      </c>
+      <c r="B928" s="6">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="C928" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="D928" s="7" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="929" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A929" s="5">
+        <v>45735</v>
+      </c>
+      <c r="B929" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C929" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D929" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="930" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A930" s="5">
+        <v>45736</v>
+      </c>
+      <c r="B930" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C930" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D930" s="7" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="931" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A931" s="5">
+        <v>45736</v>
+      </c>
+      <c r="B931" s="6">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C931" s="6">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D931" s="7" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="932" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A932" s="5">
+        <v>45736</v>
+      </c>
+      <c r="B932" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C932" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D932" s="7" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="933" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A933" s="5">
+        <v>45736</v>
+      </c>
+      <c r="B933" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C933" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D933" s="7" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="934" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A934" s="5">
+        <v>45736</v>
+      </c>
+      <c r="B934" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="C934" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D934" s="7" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="935" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A935" s="5">
+        <v>45736</v>
+      </c>
+      <c r="B935" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C935" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D935" s="7" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="936" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A936" s="5">
+        <v>45739</v>
+      </c>
+      <c r="B936" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C936" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D936" s="7" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="937" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A937" s="5">
+        <v>45739</v>
+      </c>
+      <c r="B937" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C937" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D937" s="7" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="938" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A938" s="5">
+        <v>45739</v>
+      </c>
+      <c r="B938" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="C938" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="D938" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="939" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A939" s="5">
+        <v>45739</v>
+      </c>
+      <c r="B939" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C939" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D939" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="940" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A940" s="5">
+        <v>45740</v>
+      </c>
+      <c r="B940" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C940" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D940" s="7" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="941" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A941" s="5">
+        <v>45740</v>
+      </c>
+      <c r="B941" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="C941" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D941" s="7" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="942" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A942" s="5">
+        <v>45740</v>
+      </c>
+      <c r="B942" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C942" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D942" s="7" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="943" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A943" s="5">
+        <v>45740</v>
+      </c>
+      <c r="B943" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C943" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D943" s="7" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="944" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A944" s="5">
+        <v>45740</v>
+      </c>
+      <c r="B944" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C944" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D944" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="945" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A945" s="5">
+        <v>45740</v>
+      </c>
+      <c r="B945" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C945" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D945" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="946" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A946" s="5">
+        <v>45741</v>
+      </c>
+      <c r="B946" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="C946" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D946" s="7" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="947" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A947" s="5">
+        <v>45741</v>
+      </c>
+      <c r="B947" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C947" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D947" s="7" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="948" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A948" s="5">
+        <v>45741</v>
+      </c>
+      <c r="B948" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C948" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D948" s="7" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="949" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A949" s="5">
+        <v>45742</v>
+      </c>
+      <c r="B949" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C949" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D949" s="7" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="950" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A950" s="5">
+        <v>45742</v>
+      </c>
+      <c r="B950" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C950" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D950" s="7" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="951" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A951" s="5">
+        <v>45742</v>
+      </c>
+      <c r="B951" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C951" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D951" s="7" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="952" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A952" s="5">
+        <v>45742</v>
+      </c>
+      <c r="B952" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C952" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D952" s="7" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="953" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A953" s="5">
+        <v>45743</v>
+      </c>
+      <c r="B953" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C953" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D953" s="7" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="954" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A954" s="5">
+        <v>45743</v>
+      </c>
+      <c r="B954" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C954" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D954" s="7" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="955" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A955" s="5">
+        <v>45743</v>
+      </c>
+      <c r="B955" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C955" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D955" s="7" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="956" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A956" s="5">
+        <v>45743</v>
+      </c>
+      <c r="B956" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C956" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D956" s="7" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="957" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A957" s="5">
+        <v>45744</v>
+      </c>
+      <c r="B957" s="6">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="C957" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D957" s="7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="958" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A958" s="5">
+        <v>45744</v>
+      </c>
+      <c r="B958" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C958" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D958" s="7" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="959" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A959" s="5">
+        <v>45746</v>
+      </c>
+      <c r="B959" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C959" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D959" s="7" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="960" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A960" s="5">
+        <v>45746</v>
+      </c>
+      <c r="B960" s="6">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="C960" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D960" s="7" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="961" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A961" s="5">
+        <v>45746</v>
+      </c>
+      <c r="B961" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="C961" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D961" s="7" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="962" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A962" s="5">
+        <v>45746</v>
+      </c>
+      <c r="B962" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C962" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D962" s="7" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="963" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A963" s="5">
+        <v>45746</v>
+      </c>
+      <c r="B963" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C963" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D963" s="7" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="964" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A964" s="5">
+        <v>45746</v>
+      </c>
+      <c r="B964" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="C964" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D964" s="7" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="965" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A965" s="5">
+        <v>45746</v>
+      </c>
+      <c r="B965" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C965" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D965" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="966" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A966" s="5">
+        <v>45746</v>
+      </c>
+      <c r="B966" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C966" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D966" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="967" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A967" s="5">
+        <v>45747</v>
+      </c>
+      <c r="B967" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="C967" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D967" s="7" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="968" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A968" s="5">
+        <v>45747</v>
+      </c>
+      <c r="B968" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="C968" s="6">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D968" s="7" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="969" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A969" s="5">
+        <v>45747</v>
+      </c>
+      <c r="B969" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C969" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D969" s="7" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="970" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A970" s="5">
+        <v>45747</v>
+      </c>
+      <c r="B970" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C970" s="6">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D970" s="7" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="971" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A971" s="5">
+        <v>45747</v>
+      </c>
+      <c r="B971" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="C971" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D971" s="7" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="972" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A972" s="5">
+        <v>45747</v>
+      </c>
+      <c r="B972" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="C972" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D972" s="7" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="973" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A973" s="5">
+        <v>45747</v>
+      </c>
+      <c r="B973" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="C973" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D973" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="974" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A974" s="5">
+        <v>45747</v>
+      </c>
+      <c r="B974" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="C974" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="D974" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
